--- a/dropBD/bread.xlsx
+++ b/dropBD/bread.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinapuskova/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinapuskova/Drop_Coffe/dropBD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73C76E4-08FD-094C-A4B9-7BA7E75D727D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AAAB0F3-8FCA-534B-84E6-CFD609CF5B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{0A53A493-1E76-1F47-BC5D-DEE45E5512B3}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{0A53A493-1E76-1F47-BC5D-DEE45E5512B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>bread name</t>
   </si>
@@ -78,13 +78,28 @@
   </si>
   <si>
     <t>Ржано-пшеничная булочка с отрубями, кунжутом, льном и подсолнечником. Плотная, с лёгкой сладостью солода и хрустящими семечками.</t>
+  </si>
+  <si>
+    <t>baguette.png</t>
+  </si>
+  <si>
+    <t>Mini_baguette.webp</t>
+  </si>
+  <si>
+    <t>Bagel.png</t>
+  </si>
+  <si>
+    <t>Malt_Bun.png</t>
+  </si>
+  <si>
+    <t>Alpine_bread.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -94,14 +109,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="15"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Apple Color Emoji"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color theme="1"/>
-      <name val="Apple Color Emoji"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -124,10 +135,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -462,14 +472,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A89FA52-E73D-EF4F-8542-845D4787E837}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="121.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -483,60 +494,369 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>85</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>89</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>149</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>48</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="D5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>48</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
